--- a/backend/data/financials_by_company/0106.HK.xlsx
+++ b/backend/data/financials_by_company/0106.HK.xlsx
@@ -3954,162 +3954,162 @@
       </c>
       <c r="DB1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EH1" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Zheng  Huang', 'age': 42, 'title': 'Chief Executive Officer', 'yearBorn': 1983, 'fiscalYear': 2024, 'totalPay': 1510561, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chenlong  Zhang', 'age': 47, 'title': 'Executive Chairman', 'yearBorn': 1978, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John  Ho', 'age': 43, 'title': 'VP &amp; CEO of United States', 'yearBorn': 1982, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Zheng  Huang', 'age': 42, 'title': 'Chief Executive Officer', 'yearBorn': 1983, 'fiscalYear': 2024, 'totalPay': 1506511, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chenlong  Zhang', 'age': 47, 'title': 'Executive Chairman', 'yearBorn': 1978, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John  Ho', 'age': 43, 'title': 'VP &amp; CEO of United States', 'yearBorn': 1982, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4285,7 +4285,7 @@
         <v>7.98</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.239</v>
+        <v>-0.196</v>
       </c>
       <c r="AF2" t="n">
         <v>0.02923077</v>
@@ -4324,7 +4324,7 @@
         <v>89514843</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="AS2" t="n">
         <v>0.028</v>
@@ -4365,7 +4365,7 @@
         <v>-0.87451</v>
       </c>
       <c r="BE2" t="n">
-        <v>2387173687</v>
+        <v>2599346965</v>
       </c>
       <c r="BF2" t="n">
         <v>4711307545</v>
@@ -4380,7 +4380,7 @@
         <v>4711307545</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0.36809078</v>
+        <v>-0.36710382</v>
       </c>
       <c r="BK2" t="n">
         <v>1735603200</v>
@@ -4421,7 +4421,7 @@
         <v>0.3571428</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BX2" t="n">
         <v>0.03</v>
@@ -4531,72 +4531,72 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DB2" t="n">
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>Landsea Green Management Limited</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
         <v>0</v>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DD2" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="inlineStr">
         <is>
           <t>0.018 - 0.02</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>LANDSEA MGMT</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>Landsea Green Management Limited</t>
-        </is>
-      </c>
-      <c r="DG2" t="n">
+      <c r="DI2" t="n">
         <v>0</v>
       </c>
-      <c r="DH2" t="n">
-        <v>0.005999999</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0.46153837</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>0.013 - 0.028</t>
-        </is>
+      <c r="DJ2" t="n">
+        <v>0.004999999</v>
       </c>
       <c r="DK2" t="n">
+        <v>0.35714278</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>0.014 - 0.028</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
         <v>-0.0090000015</v>
       </c>
-      <c r="DL2" t="n">
+      <c r="DN2" t="n">
         <v>-0.32142863</v>
       </c>
-      <c r="DM2" t="n">
+      <c r="DO2" t="n">
         <v>35.71428</v>
       </c>
-      <c r="DN2" t="n">
+      <c r="DP2" t="n">
         <v>1743173169</v>
       </c>
-      <c r="DO2" t="n">
+      <c r="DQ2" t="n">
         <v>1743173169</v>
       </c>
-      <c r="DP2" t="b">
+      <c r="DR2" t="b">
         <v>0</v>
       </c>
-      <c r="DQ2" t="n">
+      <c r="DS2" t="n">
         <v>-0.38</v>
       </c>
-      <c r="DR2" t="n">
+      <c r="DT2" t="n">
         <v>0.65</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
@@ -4605,45 +4605,45 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0.0516177</v>
+        <v>0</v>
       </c>
       <c r="DX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.051756475</v>
+      </c>
+      <c r="DZ2" t="n">
         <v>15</v>
       </c>
-      <c r="DY2" t="n">
+      <c r="EA2" t="n">
         <v>15</v>
       </c>
-      <c r="DZ2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>Landsea Green Properties Co., Ltd.</t>
         </is>
       </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="EB2" t="b">
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="ED2" t="b">
         <v>0</v>
       </c>
-      <c r="EC2" t="inlineStr">
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>LANDSEA MGMT</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="ED2" t="n">
+      <c r="EG2" t="n">
         <v>1756454890</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
